--- a/Data/EXCEL/Transfer/salemon/202512/2949-salemon-202512.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202512/2949-salemon-202512.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\202512\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202512\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{449E8355-FE5A-403D-9778-F702EBB93E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16D13713-F0ED-46D6-953A-DFF950CF3CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="930" windowWidth="26910" windowHeight="18975" xr2:uid="{BB469059-61F9-4DD4-8387-C575A8638C18}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="17565" windowHeight="11295" xr2:uid="{26177DBC-6E38-4DE5-9E59-3BC47DD05F9D}"/>
   </bookViews>
   <sheets>
     <sheet name="2949-salemon-202512" sheetId="2" r:id="rId1"/>
@@ -857,13 +857,13 @@
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1258,19 +1258,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DBD5FD9-2EFC-46F9-924D-29FBD238712F}">
-  <dimension ref="A1:Q43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6CDBB0-1BE3-4940-8202-A2CD678B91D2}">
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
-    <col min="2" max="5" width="12.625" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="13.875" customWidth="1"/>
-    <col min="8" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="12.625" customWidth="1"/>
-    <col min="12" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="12.625" customWidth="1"/>
-    <col min="17" max="17" width="13.75" customWidth="1"/>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
+    <col min="2" max="5" width="7.875" customWidth="1"/>
+    <col min="6" max="6" width="7.5" customWidth="1"/>
+    <col min="7" max="7" width="8.625" customWidth="1"/>
+    <col min="8" max="10" width="7.5" customWidth="1"/>
+    <col min="11" max="11" width="7.875" customWidth="1"/>
+    <col min="12" max="15" width="7.5" customWidth="1"/>
+    <col min="16" max="16" width="7.875" customWidth="1"/>
+    <col min="17" max="17" width="8.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1423,1332 +1423,1332 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B5" s="6">
-        <v>71.900000000000006</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="C5" s="6">
-        <v>69.900000000000006</v>
+        <v>67.5</v>
       </c>
       <c r="D5" s="6">
-        <v>71.900000000000006</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="E5" s="6">
-        <v>67.400000000000006</v>
+        <v>67.5</v>
       </c>
       <c r="F5" s="7">
-        <v>-2.1</v>
+        <v>-2.4</v>
       </c>
       <c r="G5" s="7">
-        <v>-2.92</v>
+        <v>-3.43</v>
       </c>
       <c r="H5" s="8">
-        <v>8.5</v>
-      </c>
-      <c r="I5" s="9">
-        <v>73.3</v>
+        <v>4.91</v>
+      </c>
+      <c r="I5" s="7">
+        <v>-42.2</v>
       </c>
       <c r="J5" s="9">
-        <v>15.3</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="K5" s="8">
-        <v>52.25</v>
+        <v>57.16</v>
       </c>
       <c r="L5" s="9">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="M5" s="8">
-        <v>8.5</v>
-      </c>
-      <c r="N5" s="9">
-        <v>73.3</v>
+        <v>4.91</v>
+      </c>
+      <c r="N5" s="7">
+        <v>-42.2</v>
       </c>
       <c r="O5" s="9">
-        <v>15.3</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="P5" s="8">
-        <v>52.25</v>
+        <v>57.16</v>
       </c>
       <c r="Q5" s="9">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B6" s="12">
-        <v>74.599999999999994</v>
+        <v>71.900000000000006</v>
       </c>
       <c r="C6" s="12">
-        <v>72</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="D6" s="12">
-        <v>77</v>
+        <v>71.900000000000006</v>
       </c>
       <c r="E6" s="12">
-        <v>70.599999999999994</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="F6" s="13">
-        <v>1.6</v>
+        <v>-2.1</v>
       </c>
       <c r="G6" s="13">
-        <v>2.27</v>
+        <v>-2.92</v>
       </c>
       <c r="H6" s="14">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="I6" s="13">
-        <v>4.03</v>
-      </c>
-      <c r="J6" s="13">
-        <v>28.3</v>
+        <v>8.5</v>
+      </c>
+      <c r="I6" s="15">
+        <v>73.3</v>
+      </c>
+      <c r="J6" s="15">
+        <v>15.3</v>
       </c>
       <c r="K6" s="14">
-        <v>43.76</v>
-      </c>
-      <c r="L6" s="13">
-        <v>23.1</v>
+        <v>52.25</v>
+      </c>
+      <c r="L6" s="15">
+        <v>21.8</v>
       </c>
       <c r="M6" s="14">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="N6" s="13">
-        <v>4.03</v>
-      </c>
-      <c r="O6" s="13">
-        <v>28.3</v>
+        <v>8.5</v>
+      </c>
+      <c r="N6" s="15">
+        <v>73.3</v>
+      </c>
+      <c r="O6" s="15">
+        <v>15.3</v>
       </c>
       <c r="P6" s="14">
-        <v>43.76</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>23.1</v>
+        <v>52.25</v>
+      </c>
+      <c r="Q6" s="15">
+        <v>21.8</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B7" s="6">
-        <v>82.1</v>
+        <v>74.599999999999994</v>
       </c>
       <c r="C7" s="6">
-        <v>70.400000000000006</v>
+        <v>72</v>
       </c>
       <c r="D7" s="6">
-        <v>82.3</v>
+        <v>77</v>
       </c>
       <c r="E7" s="6">
-        <v>67</v>
-      </c>
-      <c r="F7" s="7">
-        <v>-12.3</v>
-      </c>
-      <c r="G7" s="7">
-        <v>-14.87</v>
+        <v>70.599999999999994</v>
+      </c>
+      <c r="F7" s="9">
+        <v>1.6</v>
+      </c>
+      <c r="G7" s="9">
+        <v>2.27</v>
       </c>
       <c r="H7" s="8">
-        <v>4.71</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I7" s="9">
-        <v>5.3</v>
+        <v>4.03</v>
       </c>
       <c r="J7" s="9">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="K7" s="8">
-        <v>38.86</v>
+        <v>43.76</v>
       </c>
       <c r="L7" s="9">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="M7" s="8">
-        <v>4.71</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="N7" s="9">
-        <v>5.3</v>
+        <v>4.03</v>
       </c>
       <c r="O7" s="9">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="P7" s="8">
-        <v>38.86</v>
+        <v>43.76</v>
       </c>
       <c r="Q7" s="9">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B8" s="12">
-        <v>81.7</v>
+        <v>82.1</v>
       </c>
       <c r="C8" s="12">
-        <v>82.7</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="D8" s="12">
-        <v>87</v>
+        <v>82.3</v>
       </c>
       <c r="E8" s="12">
-        <v>80</v>
-      </c>
-      <c r="F8" s="15">
-        <v>-0.3</v>
-      </c>
-      <c r="G8" s="15">
-        <v>-0.36</v>
+        <v>67</v>
+      </c>
+      <c r="F8" s="13">
+        <v>-12.3</v>
+      </c>
+      <c r="G8" s="13">
+        <v>-14.87</v>
       </c>
       <c r="H8" s="14">
-        <v>4.47</v>
-      </c>
-      <c r="I8" s="13">
-        <v>11.6</v>
-      </c>
-      <c r="J8" s="13">
+        <v>4.71</v>
+      </c>
+      <c r="I8" s="15">
+        <v>5.3</v>
+      </c>
+      <c r="J8" s="15">
+        <v>28.5</v>
+      </c>
+      <c r="K8" s="14">
+        <v>38.86</v>
+      </c>
+      <c r="L8" s="15">
         <v>22.4</v>
       </c>
-      <c r="K8" s="14">
-        <v>34.14</v>
-      </c>
-      <c r="L8" s="13">
-        <v>21.7</v>
-      </c>
       <c r="M8" s="14">
-        <v>4.47</v>
-      </c>
-      <c r="N8" s="13">
-        <v>11.6</v>
-      </c>
-      <c r="O8" s="13">
+        <v>4.71</v>
+      </c>
+      <c r="N8" s="15">
+        <v>5.3</v>
+      </c>
+      <c r="O8" s="15">
+        <v>28.5</v>
+      </c>
+      <c r="P8" s="14">
+        <v>38.86</v>
+      </c>
+      <c r="Q8" s="15">
         <v>22.4</v>
-      </c>
-      <c r="P8" s="14">
-        <v>34.14</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>21.7</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B9" s="6">
-        <v>82.1</v>
+        <v>81.7</v>
       </c>
       <c r="C9" s="6">
-        <v>83</v>
+        <v>82.7</v>
       </c>
       <c r="D9" s="6">
-        <v>85.9</v>
+        <v>87</v>
       </c>
       <c r="E9" s="6">
-        <v>81.5</v>
-      </c>
-      <c r="F9" s="9">
-        <v>0.9</v>
-      </c>
-      <c r="G9" s="9">
-        <v>1.1000000000000001</v>
+        <v>80</v>
+      </c>
+      <c r="F9" s="7">
+        <v>-0.3</v>
+      </c>
+      <c r="G9" s="7">
+        <v>-0.36</v>
       </c>
       <c r="H9" s="8">
-        <v>4.01</v>
-      </c>
-      <c r="I9" s="7">
-        <v>-19.399999999999999</v>
+        <v>4.47</v>
+      </c>
+      <c r="I9" s="9">
+        <v>11.6</v>
       </c>
       <c r="J9" s="9">
-        <v>20.399999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="K9" s="8">
-        <v>29.67</v>
+        <v>34.14</v>
       </c>
       <c r="L9" s="9">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="M9" s="8">
-        <v>4.01</v>
-      </c>
-      <c r="N9" s="7">
-        <v>-19.399999999999999</v>
+        <v>4.47</v>
+      </c>
+      <c r="N9" s="9">
+        <v>11.6</v>
       </c>
       <c r="O9" s="9">
-        <v>20.399999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="P9" s="8">
-        <v>29.67</v>
+        <v>34.14</v>
       </c>
       <c r="Q9" s="9">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B10" s="12">
-        <v>84.9</v>
+        <v>82.1</v>
       </c>
       <c r="C10" s="12">
-        <v>82.1</v>
+        <v>83</v>
       </c>
       <c r="D10" s="12">
-        <v>90</v>
+        <v>85.9</v>
       </c>
       <c r="E10" s="12">
-        <v>82.1</v>
+        <v>81.5</v>
       </c>
       <c r="F10" s="15">
-        <v>-2.8</v>
+        <v>0.9</v>
       </c>
       <c r="G10" s="15">
-        <v>-3.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H10" s="14">
-        <v>4.97</v>
+        <v>4.01</v>
       </c>
       <c r="I10" s="13">
-        <v>7.47</v>
-      </c>
-      <c r="J10" s="13">
-        <v>22.4</v>
+        <v>-19.399999999999999</v>
+      </c>
+      <c r="J10" s="15">
+        <v>20.399999999999999</v>
       </c>
       <c r="K10" s="14">
-        <v>25.66</v>
-      </c>
-      <c r="L10" s="13">
-        <v>21.7</v>
+        <v>29.67</v>
+      </c>
+      <c r="L10" s="15">
+        <v>21.5</v>
       </c>
       <c r="M10" s="14">
-        <v>4.97</v>
+        <v>4.01</v>
       </c>
       <c r="N10" s="13">
-        <v>7.47</v>
-      </c>
-      <c r="O10" s="13">
-        <v>22.4</v>
+        <v>-19.399999999999999</v>
+      </c>
+      <c r="O10" s="15">
+        <v>20.399999999999999</v>
       </c>
       <c r="P10" s="14">
-        <v>25.66</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>21.7</v>
+        <v>29.67</v>
+      </c>
+      <c r="Q10" s="15">
+        <v>21.5</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B11" s="6">
-        <v>86</v>
+        <v>84.9</v>
       </c>
       <c r="C11" s="6">
-        <v>84.9</v>
+        <v>82.1</v>
       </c>
       <c r="D11" s="6">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E11" s="6">
-        <v>84.9</v>
+        <v>82.1</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.1</v>
+        <v>-2.8</v>
       </c>
       <c r="G11" s="7">
-        <v>-0.12</v>
+        <v>-3.3</v>
       </c>
       <c r="H11" s="8">
-        <v>4.63</v>
+        <v>4.97</v>
       </c>
       <c r="I11" s="9">
-        <v>13.7</v>
+        <v>7.47</v>
       </c>
       <c r="J11" s="9">
-        <v>15.7</v>
+        <v>22.4</v>
       </c>
       <c r="K11" s="8">
-        <v>20.69</v>
+        <v>25.66</v>
       </c>
       <c r="L11" s="9">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="M11" s="8">
-        <v>4.63</v>
+        <v>4.97</v>
       </c>
       <c r="N11" s="9">
-        <v>13.7</v>
+        <v>7.47</v>
       </c>
       <c r="O11" s="9">
-        <v>15.7</v>
+        <v>22.4</v>
       </c>
       <c r="P11" s="8">
-        <v>20.69</v>
+        <v>25.66</v>
       </c>
       <c r="Q11" s="9">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B12" s="12">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C12" s="12">
-        <v>85</v>
+        <v>84.9</v>
       </c>
       <c r="D12" s="12">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E12" s="12">
-        <v>75.099999999999994</v>
+        <v>84.9</v>
       </c>
       <c r="F12" s="13">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="G12" s="13">
-        <v>0.47</v>
+        <v>-0.12</v>
       </c>
       <c r="H12" s="14">
-        <v>4.07</v>
+        <v>4.63</v>
       </c>
       <c r="I12" s="15">
-        <v>-7.42</v>
-      </c>
-      <c r="J12" s="13">
-        <v>32.799999999999997</v>
+        <v>13.7</v>
+      </c>
+      <c r="J12" s="15">
+        <v>15.7</v>
       </c>
       <c r="K12" s="14">
-        <v>16.059999999999999</v>
-      </c>
-      <c r="L12" s="13">
-        <v>23.4</v>
+        <v>20.69</v>
+      </c>
+      <c r="L12" s="15">
+        <v>21.6</v>
       </c>
       <c r="M12" s="14">
-        <v>4.07</v>
+        <v>4.63</v>
       </c>
       <c r="N12" s="15">
-        <v>-7.42</v>
-      </c>
-      <c r="O12" s="13">
-        <v>32.799999999999997</v>
+        <v>13.7</v>
+      </c>
+      <c r="O12" s="15">
+        <v>15.7</v>
       </c>
       <c r="P12" s="14">
-        <v>16.059999999999999</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>23.4</v>
+        <v>20.69</v>
+      </c>
+      <c r="Q12" s="15">
+        <v>21.6</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B13" s="6">
-        <v>79.599999999999994</v>
+        <v>84</v>
       </c>
       <c r="C13" s="6">
-        <v>84.6</v>
+        <v>85</v>
       </c>
       <c r="D13" s="6">
-        <v>91.8</v>
+        <v>90</v>
       </c>
       <c r="E13" s="6">
-        <v>76.7</v>
+        <v>75.099999999999994</v>
       </c>
       <c r="F13" s="9">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="G13" s="9">
-        <v>3.17</v>
+        <v>0.47</v>
       </c>
       <c r="H13" s="8">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="I13" s="9">
-        <v>6.4</v>
+        <v>4.07</v>
+      </c>
+      <c r="I13" s="7">
+        <v>-7.42</v>
       </c>
       <c r="J13" s="9">
-        <v>22.6</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="K13" s="8">
-        <v>11.99</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="L13" s="9">
-        <v>20.5</v>
+        <v>23.4</v>
       </c>
       <c r="M13" s="8">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="N13" s="9">
-        <v>6.4</v>
+        <v>4.07</v>
+      </c>
+      <c r="N13" s="7">
+        <v>-7.42</v>
       </c>
       <c r="O13" s="9">
-        <v>22.6</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="P13" s="8">
-        <v>11.99</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="Q13" s="9">
-        <v>20.5</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B14" s="12">
-        <v>82.7</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="C14" s="12">
-        <v>82</v>
+        <v>84.6</v>
       </c>
       <c r="D14" s="12">
-        <v>83.4</v>
+        <v>91.8</v>
       </c>
       <c r="E14" s="12">
-        <v>78.3</v>
+        <v>76.7</v>
       </c>
       <c r="F14" s="15">
-        <v>-0.9</v>
+        <v>2.6</v>
       </c>
       <c r="G14" s="15">
-        <v>-1.0900000000000001</v>
+        <v>3.17</v>
       </c>
       <c r="H14" s="14">
-        <v>4.13</v>
-      </c>
-      <c r="I14" s="13">
-        <v>19.5</v>
-      </c>
-      <c r="J14" s="13">
-        <v>39.4</v>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I14" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="J14" s="15">
+        <v>22.6</v>
       </c>
       <c r="K14" s="14">
-        <v>7.59</v>
-      </c>
-      <c r="L14" s="13">
-        <v>19.2</v>
+        <v>11.99</v>
+      </c>
+      <c r="L14" s="15">
+        <v>20.5</v>
       </c>
       <c r="M14" s="14">
-        <v>4.13</v>
-      </c>
-      <c r="N14" s="13">
-        <v>19.5</v>
-      </c>
-      <c r="O14" s="13">
-        <v>39.4</v>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="N14" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="O14" s="15">
+        <v>22.6</v>
       </c>
       <c r="P14" s="14">
-        <v>7.59</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>19.2</v>
+        <v>11.99</v>
+      </c>
+      <c r="Q14" s="15">
+        <v>20.5</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B15" s="6">
-        <v>81.599999999999994</v>
+        <v>82.7</v>
       </c>
       <c r="C15" s="6">
-        <v>82.9</v>
+        <v>82</v>
       </c>
       <c r="D15" s="6">
-        <v>86.4</v>
+        <v>83.4</v>
       </c>
       <c r="E15" s="6">
         <v>78.3</v>
       </c>
-      <c r="F15" s="9">
-        <v>1.3</v>
-      </c>
-      <c r="G15" s="9">
-        <v>1.59</v>
+      <c r="F15" s="7">
+        <v>-0.9</v>
+      </c>
+      <c r="G15" s="7">
+        <v>-1.0900000000000001</v>
       </c>
       <c r="H15" s="8">
-        <v>3.46</v>
-      </c>
-      <c r="I15" s="7">
-        <v>-18.100000000000001</v>
+        <v>4.13</v>
+      </c>
+      <c r="I15" s="9">
+        <v>19.5</v>
       </c>
       <c r="J15" s="9">
-        <v>1.66</v>
+        <v>39.4</v>
       </c>
       <c r="K15" s="8">
-        <v>3.46</v>
+        <v>7.59</v>
       </c>
       <c r="L15" s="9">
-        <v>1.66</v>
+        <v>19.2</v>
       </c>
       <c r="M15" s="8">
-        <v>3.46</v>
-      </c>
-      <c r="N15" s="7">
-        <v>-18.100000000000001</v>
+        <v>4.13</v>
+      </c>
+      <c r="N15" s="9">
+        <v>19.5</v>
       </c>
       <c r="O15" s="9">
-        <v>1.66</v>
+        <v>39.4</v>
       </c>
       <c r="P15" s="8">
-        <v>3.46</v>
+        <v>7.59</v>
       </c>
       <c r="Q15" s="9">
-        <v>1.66</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B16" s="12">
-        <v>95.4</v>
+        <v>81.599999999999994</v>
       </c>
       <c r="C16" s="12">
-        <v>81.599999999999994</v>
+        <v>82.9</v>
       </c>
       <c r="D16" s="12">
-        <v>97.8</v>
+        <v>86.4</v>
       </c>
       <c r="E16" s="12">
-        <v>78.099999999999994</v>
+        <v>78.3</v>
       </c>
       <c r="F16" s="15">
-        <v>-18.3</v>
+        <v>1.3</v>
       </c>
       <c r="G16" s="15">
-        <v>-18.32</v>
+        <v>1.59</v>
       </c>
       <c r="H16" s="14">
-        <v>4.22</v>
-      </c>
-      <c r="I16" s="15">
-        <v>-42.6</v>
-      </c>
-      <c r="J16" s="13">
-        <v>26.4</v>
+        <v>3.46</v>
+      </c>
+      <c r="I16" s="13">
+        <v>-18.100000000000001</v>
+      </c>
+      <c r="J16" s="15">
+        <v>1.66</v>
       </c>
       <c r="K16" s="14">
-        <v>47.15</v>
-      </c>
-      <c r="L16" s="13">
-        <v>8.64</v>
+        <v>3.46</v>
+      </c>
+      <c r="L16" s="15">
+        <v>1.66</v>
       </c>
       <c r="M16" s="14">
-        <v>4.22</v>
-      </c>
-      <c r="N16" s="15">
-        <v>-42.6</v>
-      </c>
-      <c r="O16" s="13">
-        <v>26.4</v>
+        <v>3.46</v>
+      </c>
+      <c r="N16" s="13">
+        <v>-18.100000000000001</v>
+      </c>
+      <c r="O16" s="15">
+        <v>1.66</v>
       </c>
       <c r="P16" s="14">
-        <v>47.15</v>
-      </c>
-      <c r="Q16" s="13">
-        <v>8.64</v>
+        <v>3.46</v>
+      </c>
+      <c r="Q16" s="15">
+        <v>1.66</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>45597</v>
+        <v>45627</v>
       </c>
       <c r="B17" s="6">
-        <v>84.9</v>
+        <v>95.4</v>
       </c>
       <c r="C17" s="6">
-        <v>99.9</v>
+        <v>81.599999999999994</v>
       </c>
       <c r="D17" s="6">
-        <v>102.5</v>
+        <v>97.8</v>
       </c>
       <c r="E17" s="6">
-        <v>84</v>
-      </c>
-      <c r="F17" s="9">
-        <v>15</v>
-      </c>
-      <c r="G17" s="9">
-        <v>17.670000000000002</v>
+        <v>78.099999999999994</v>
+      </c>
+      <c r="F17" s="7">
+        <v>-18.3</v>
+      </c>
+      <c r="G17" s="7">
+        <v>-18.32</v>
       </c>
       <c r="H17" s="8">
-        <v>7.37</v>
-      </c>
-      <c r="I17" s="9">
-        <v>92.8</v>
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="I17" s="7">
+        <v>-42.6</v>
       </c>
       <c r="J17" s="9">
-        <v>18.600000000000001</v>
+        <v>26.6</v>
       </c>
       <c r="K17" s="8">
-        <v>42.92</v>
+        <v>47.15</v>
       </c>
       <c r="L17" s="9">
-        <v>7.14</v>
+        <v>8.64</v>
       </c>
       <c r="M17" s="8">
-        <v>7.37</v>
-      </c>
-      <c r="N17" s="9">
-        <v>92.8</v>
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="N17" s="7">
+        <v>-42.6</v>
       </c>
       <c r="O17" s="9">
-        <v>18.600000000000001</v>
+        <v>26.6</v>
       </c>
       <c r="P17" s="8">
-        <v>42.92</v>
+        <v>47.15</v>
       </c>
       <c r="Q17" s="9">
-        <v>7.14</v>
+        <v>8.64</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B18" s="12">
-        <v>80.5</v>
+        <v>84.9</v>
       </c>
       <c r="C18" s="12">
-        <v>84.9</v>
+        <v>99.9</v>
       </c>
       <c r="D18" s="12">
-        <v>96</v>
+        <v>102.5</v>
       </c>
       <c r="E18" s="12">
-        <v>80.5</v>
-      </c>
-      <c r="F18" s="13">
-        <v>3.4</v>
-      </c>
-      <c r="G18" s="13">
-        <v>4.17</v>
+        <v>84</v>
+      </c>
+      <c r="F18" s="15">
+        <v>15</v>
+      </c>
+      <c r="G18" s="15">
+        <v>17.670000000000002</v>
       </c>
       <c r="H18" s="14">
-        <v>3.82</v>
-      </c>
-      <c r="I18" s="13">
-        <v>3.37</v>
-      </c>
-      <c r="J18" s="13">
-        <v>5.22</v>
+        <v>7.37</v>
+      </c>
+      <c r="I18" s="15">
+        <v>92.8</v>
+      </c>
+      <c r="J18" s="15">
+        <v>18.600000000000001</v>
       </c>
       <c r="K18" s="14">
-        <v>35.549999999999997</v>
-      </c>
-      <c r="L18" s="13">
-        <v>5.03</v>
+        <v>42.92</v>
+      </c>
+      <c r="L18" s="15">
+        <v>7.14</v>
       </c>
       <c r="M18" s="14">
-        <v>3.82</v>
-      </c>
-      <c r="N18" s="13">
-        <v>3.37</v>
-      </c>
-      <c r="O18" s="13">
-        <v>5.22</v>
+        <v>7.37</v>
+      </c>
+      <c r="N18" s="15">
+        <v>92.8</v>
+      </c>
+      <c r="O18" s="15">
+        <v>18.600000000000001</v>
       </c>
       <c r="P18" s="14">
-        <v>35.549999999999997</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>5.03</v>
+        <v>42.92</v>
+      </c>
+      <c r="Q18" s="15">
+        <v>7.14</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B19" s="6">
-        <v>89</v>
+        <v>80.5</v>
       </c>
       <c r="C19" s="6">
-        <v>81.5</v>
+        <v>84.9</v>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E19" s="6">
-        <v>80</v>
-      </c>
-      <c r="F19" s="7">
-        <v>-6.1</v>
-      </c>
-      <c r="G19" s="7">
-        <v>-6.96</v>
+        <v>80.5</v>
+      </c>
+      <c r="F19" s="9">
+        <v>3.4</v>
+      </c>
+      <c r="G19" s="9">
+        <v>4.17</v>
       </c>
       <c r="H19" s="8">
-        <v>3.67</v>
+        <v>3.82</v>
       </c>
       <c r="I19" s="9">
-        <v>0.35</v>
-      </c>
-      <c r="J19" s="7">
-        <v>-4.12</v>
+        <v>3.37</v>
+      </c>
+      <c r="J19" s="9">
+        <v>5.22</v>
       </c>
       <c r="K19" s="8">
-        <v>31.73</v>
+        <v>35.549999999999997</v>
       </c>
       <c r="L19" s="9">
-        <v>5.01</v>
+        <v>5.03</v>
       </c>
       <c r="M19" s="8">
-        <v>3.67</v>
+        <v>3.82</v>
       </c>
       <c r="N19" s="9">
-        <v>0.35</v>
-      </c>
-      <c r="O19" s="7">
-        <v>-4.12</v>
+        <v>3.37</v>
+      </c>
+      <c r="O19" s="9">
+        <v>5.22</v>
       </c>
       <c r="P19" s="8">
-        <v>31.73</v>
+        <v>35.549999999999997</v>
       </c>
       <c r="Q19" s="9">
-        <v>5.01</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B20" s="12">
-        <v>91.6</v>
+        <v>89</v>
       </c>
       <c r="C20" s="12">
-        <v>87.6</v>
+        <v>81.5</v>
       </c>
       <c r="D20" s="12">
-        <v>91.6</v>
+        <v>90</v>
       </c>
       <c r="E20" s="12">
-        <v>76.7</v>
-      </c>
-      <c r="F20" s="15">
-        <v>-2.5</v>
-      </c>
-      <c r="G20" s="15">
-        <v>-2.77</v>
+        <v>80</v>
+      </c>
+      <c r="F20" s="13">
+        <v>-6.1</v>
+      </c>
+      <c r="G20" s="13">
+        <v>-6.96</v>
       </c>
       <c r="H20" s="14">
-        <v>3.65</v>
-      </c>
-      <c r="I20" s="13">
-        <v>9.76</v>
+        <v>3.67</v>
+      </c>
+      <c r="I20" s="15">
+        <v>0.35</v>
       </c>
       <c r="J20" s="13">
-        <v>7.48</v>
+        <v>-4.12</v>
       </c>
       <c r="K20" s="14">
-        <v>28.07</v>
-      </c>
-      <c r="L20" s="13">
-        <v>6.33</v>
+        <v>31.73</v>
+      </c>
+      <c r="L20" s="15">
+        <v>5.01</v>
       </c>
       <c r="M20" s="14">
-        <v>3.65</v>
-      </c>
-      <c r="N20" s="13">
-        <v>9.76</v>
+        <v>3.67</v>
+      </c>
+      <c r="N20" s="15">
+        <v>0.35</v>
       </c>
       <c r="O20" s="13">
-        <v>7.48</v>
+        <v>-4.12</v>
       </c>
       <c r="P20" s="14">
-        <v>28.07</v>
-      </c>
-      <c r="Q20" s="13">
-        <v>6.33</v>
+        <v>31.73</v>
+      </c>
+      <c r="Q20" s="15">
+        <v>5.01</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B21" s="6">
-        <v>94.7</v>
+        <v>91.6</v>
       </c>
       <c r="C21" s="6">
-        <v>90.1</v>
+        <v>87.6</v>
       </c>
       <c r="D21" s="6">
-        <v>95.7</v>
+        <v>91.6</v>
       </c>
       <c r="E21" s="6">
-        <v>90.1</v>
+        <v>76.7</v>
       </c>
       <c r="F21" s="7">
-        <v>-5.3</v>
+        <v>-2.5</v>
       </c>
       <c r="G21" s="7">
-        <v>-5.56</v>
+        <v>-2.77</v>
       </c>
       <c r="H21" s="8">
-        <v>3.33</v>
-      </c>
-      <c r="I21" s="7">
-        <v>-17.7</v>
+        <v>3.65</v>
+      </c>
+      <c r="I21" s="9">
+        <v>9.76</v>
       </c>
       <c r="J21" s="9">
-        <v>4.18</v>
+        <v>7.48</v>
       </c>
       <c r="K21" s="8">
-        <v>24.41</v>
+        <v>28.07</v>
       </c>
       <c r="L21" s="9">
-        <v>6.16</v>
+        <v>6.33</v>
       </c>
       <c r="M21" s="8">
-        <v>3.33</v>
-      </c>
-      <c r="N21" s="7">
-        <v>-17.7</v>
+        <v>3.65</v>
+      </c>
+      <c r="N21" s="9">
+        <v>9.76</v>
       </c>
       <c r="O21" s="9">
-        <v>4.18</v>
+        <v>7.48</v>
       </c>
       <c r="P21" s="8">
-        <v>24.41</v>
+        <v>28.07</v>
       </c>
       <c r="Q21" s="9">
-        <v>6.16</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B22" s="12">
-        <v>96.1</v>
+        <v>94.7</v>
       </c>
       <c r="C22" s="12">
-        <v>95.4</v>
+        <v>90.1</v>
       </c>
       <c r="D22" s="12">
-        <v>99.3</v>
+        <v>95.7</v>
       </c>
       <c r="E22" s="12">
-        <v>93</v>
-      </c>
-      <c r="F22" s="15">
-        <v>-1</v>
-      </c>
-      <c r="G22" s="15">
-        <v>-1.04</v>
+        <v>90.1</v>
+      </c>
+      <c r="F22" s="13">
+        <v>-5.3</v>
+      </c>
+      <c r="G22" s="13">
+        <v>-5.56</v>
       </c>
       <c r="H22" s="14">
-        <v>4.07</v>
+        <v>3.33</v>
       </c>
       <c r="I22" s="13">
-        <v>1.61</v>
-      </c>
-      <c r="J22" s="13">
-        <v>2.44</v>
+        <v>-17.7</v>
+      </c>
+      <c r="J22" s="15">
+        <v>4.18</v>
       </c>
       <c r="K22" s="14">
-        <v>21.08</v>
-      </c>
-      <c r="L22" s="13">
-        <v>6.48</v>
+        <v>24.41</v>
+      </c>
+      <c r="L22" s="15">
+        <v>6.16</v>
       </c>
       <c r="M22" s="14">
-        <v>4.07</v>
+        <v>3.33</v>
       </c>
       <c r="N22" s="13">
-        <v>1.61</v>
-      </c>
-      <c r="O22" s="13">
-        <v>2.44</v>
+        <v>-17.7</v>
+      </c>
+      <c r="O22" s="15">
+        <v>4.18</v>
       </c>
       <c r="P22" s="14">
-        <v>21.08</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>6.48</v>
+        <v>24.41</v>
+      </c>
+      <c r="Q22" s="15">
+        <v>6.16</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B23" s="6">
-        <v>104</v>
+        <v>96.1</v>
       </c>
       <c r="C23" s="6">
-        <v>96.4</v>
+        <v>95.4</v>
       </c>
       <c r="D23" s="6">
-        <v>105</v>
+        <v>99.3</v>
       </c>
       <c r="E23" s="6">
-        <v>96.4</v>
+        <v>93</v>
       </c>
       <c r="F23" s="7">
-        <v>-8.1</v>
+        <v>-1</v>
       </c>
       <c r="G23" s="7">
-        <v>-7.75</v>
+        <v>-1.04</v>
       </c>
       <c r="H23" s="8">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="I23" s="9">
-        <v>30.6</v>
+        <v>1.61</v>
       </c>
       <c r="J23" s="9">
-        <v>4.24</v>
+        <v>2.44</v>
       </c>
       <c r="K23" s="8">
-        <v>17.02</v>
+        <v>21.08</v>
       </c>
       <c r="L23" s="9">
-        <v>7.48</v>
+        <v>6.48</v>
       </c>
       <c r="M23" s="8">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="N23" s="9">
-        <v>30.6</v>
+        <v>1.61</v>
       </c>
       <c r="O23" s="9">
-        <v>4.24</v>
+        <v>2.44</v>
       </c>
       <c r="P23" s="8">
-        <v>17.02</v>
+        <v>21.08</v>
       </c>
       <c r="Q23" s="9">
-        <v>7.48</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B24" s="12">
-        <v>109.5</v>
+        <v>104</v>
       </c>
       <c r="C24" s="12">
-        <v>104.5</v>
+        <v>96.4</v>
       </c>
       <c r="D24" s="12">
-        <v>111.5</v>
+        <v>105</v>
       </c>
       <c r="E24" s="12">
-        <v>101</v>
-      </c>
-      <c r="F24" s="15">
-        <v>-5</v>
-      </c>
-      <c r="G24" s="15">
-        <v>-4.57</v>
+        <v>96.4</v>
+      </c>
+      <c r="F24" s="13">
+        <v>-8.1</v>
+      </c>
+      <c r="G24" s="13">
+        <v>-7.75</v>
       </c>
       <c r="H24" s="14">
-        <v>3.06</v>
+        <v>4</v>
       </c>
       <c r="I24" s="15">
-        <v>-14.3</v>
-      </c>
-      <c r="J24" s="13">
-        <v>10</v>
+        <v>30.6</v>
+      </c>
+      <c r="J24" s="15">
+        <v>4.24</v>
       </c>
       <c r="K24" s="14">
-        <v>13.02</v>
-      </c>
-      <c r="L24" s="13">
-        <v>8.52</v>
+        <v>17.02</v>
+      </c>
+      <c r="L24" s="15">
+        <v>7.48</v>
       </c>
       <c r="M24" s="14">
-        <v>3.06</v>
+        <v>4</v>
       </c>
       <c r="N24" s="15">
-        <v>-14.3</v>
-      </c>
-      <c r="O24" s="13">
-        <v>10</v>
+        <v>30.6</v>
+      </c>
+      <c r="O24" s="15">
+        <v>4.24</v>
       </c>
       <c r="P24" s="14">
-        <v>13.02</v>
-      </c>
-      <c r="Q24" s="13">
-        <v>8.52</v>
+        <v>17.02</v>
+      </c>
+      <c r="Q24" s="15">
+        <v>7.48</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B25" s="6">
+        <v>109.5</v>
+      </c>
+      <c r="C25" s="6">
         <v>104.5</v>
       </c>
-      <c r="C25" s="6">
-        <v>109.5</v>
-      </c>
       <c r="D25" s="6">
-        <v>117.5</v>
+        <v>111.5</v>
       </c>
       <c r="E25" s="6">
-        <v>103</v>
-      </c>
-      <c r="F25" s="9">
-        <v>4.5</v>
-      </c>
-      <c r="G25" s="9">
-        <v>4.29</v>
+        <v>101</v>
+      </c>
+      <c r="F25" s="7">
+        <v>-5</v>
+      </c>
+      <c r="G25" s="7">
+        <v>-4.57</v>
       </c>
       <c r="H25" s="8">
-        <v>3.59</v>
-      </c>
-      <c r="I25" s="9">
-        <v>20.9</v>
+        <v>3.06</v>
+      </c>
+      <c r="I25" s="7">
+        <v>-14.3</v>
       </c>
       <c r="J25" s="9">
-        <v>2.75</v>
+        <v>10</v>
       </c>
       <c r="K25" s="8">
-        <v>9.9499999999999993</v>
+        <v>13.02</v>
       </c>
       <c r="L25" s="9">
-        <v>8.08</v>
+        <v>8.52</v>
       </c>
       <c r="M25" s="8">
-        <v>3.59</v>
-      </c>
-      <c r="N25" s="9">
-        <v>20.9</v>
+        <v>3.06</v>
+      </c>
+      <c r="N25" s="7">
+        <v>-14.3</v>
       </c>
       <c r="O25" s="9">
-        <v>2.75</v>
+        <v>10</v>
       </c>
       <c r="P25" s="8">
-        <v>9.9499999999999993</v>
+        <v>13.02</v>
       </c>
       <c r="Q25" s="9">
-        <v>8.08</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B26" s="12">
+        <v>104.5</v>
+      </c>
+      <c r="C26" s="12">
+        <v>109.5</v>
+      </c>
+      <c r="D26" s="12">
+        <v>117.5</v>
+      </c>
+      <c r="E26" s="12">
         <v>103</v>
       </c>
-      <c r="C26" s="12">
-        <v>105</v>
-      </c>
-      <c r="D26" s="12">
-        <v>124</v>
-      </c>
-      <c r="E26" s="12">
-        <v>102.5</v>
-      </c>
-      <c r="F26" s="13">
-        <v>3</v>
-      </c>
-      <c r="G26" s="13">
-        <v>2.94</v>
+      <c r="F26" s="15">
+        <v>4.5</v>
+      </c>
+      <c r="G26" s="15">
+        <v>4.29</v>
       </c>
       <c r="H26" s="14">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="I26" s="15">
-        <v>-12.8</v>
-      </c>
-      <c r="J26" s="13">
-        <v>5.54</v>
+        <v>20.9</v>
+      </c>
+      <c r="J26" s="15">
+        <v>2.75</v>
       </c>
       <c r="K26" s="14">
-        <v>6.37</v>
-      </c>
-      <c r="L26" s="13">
-        <v>11.3</v>
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="L26" s="15">
+        <v>8.08</v>
       </c>
       <c r="M26" s="14">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="N26" s="15">
-        <v>-12.8</v>
-      </c>
-      <c r="O26" s="13">
-        <v>5.54</v>
+        <v>20.9</v>
+      </c>
+      <c r="O26" s="15">
+        <v>2.75</v>
       </c>
       <c r="P26" s="14">
-        <v>6.37</v>
-      </c>
-      <c r="Q26" s="13">
-        <v>11.3</v>
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="Q26" s="15">
+        <v>8.08</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B27" s="6">
-        <v>122.5</v>
+        <v>103</v>
       </c>
       <c r="C27" s="6">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D27" s="6">
-        <v>126.5</v>
+        <v>124</v>
       </c>
       <c r="E27" s="6">
-        <v>100</v>
-      </c>
-      <c r="F27" s="7">
-        <v>-19</v>
-      </c>
-      <c r="G27" s="7">
-        <v>-15.7</v>
+        <v>102.5</v>
+      </c>
+      <c r="F27" s="9">
+        <v>3</v>
+      </c>
+      <c r="G27" s="9">
+        <v>2.94</v>
       </c>
       <c r="H27" s="8">
-        <v>3.4</v>
-      </c>
-      <c r="I27" s="9">
-        <v>2.36</v>
+        <v>2.97</v>
+      </c>
+      <c r="I27" s="7">
+        <v>-12.8</v>
       </c>
       <c r="J27" s="9">
-        <v>16.899999999999999</v>
+        <v>5.54</v>
       </c>
       <c r="K27" s="8">
-        <v>3.4</v>
+        <v>6.37</v>
       </c>
       <c r="L27" s="9">
-        <v>16.899999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="M27" s="8">
-        <v>3.4</v>
-      </c>
-      <c r="N27" s="9">
-        <v>2.36</v>
+        <v>2.97</v>
+      </c>
+      <c r="N27" s="7">
+        <v>-12.8</v>
       </c>
       <c r="O27" s="9">
-        <v>16.899999999999999</v>
+        <v>5.54</v>
       </c>
       <c r="P27" s="8">
-        <v>3.4</v>
+        <v>6.37</v>
       </c>
       <c r="Q27" s="9">
-        <v>16.899999999999999</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B28" s="12">
-        <v>142.5</v>
+        <v>122.5</v>
       </c>
       <c r="C28" s="12">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="D28" s="12">
-        <v>165</v>
+        <v>126.5</v>
       </c>
       <c r="E28" s="12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F28" s="13">
-        <v>31</v>
+        <v>-19</v>
       </c>
       <c r="G28" s="13">
-        <v>34.44</v>
+        <v>-15.7</v>
       </c>
       <c r="H28" s="14">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="I28" s="15">
-        <v>-46.2</v>
+        <v>2.36</v>
       </c>
       <c r="J28" s="15">
-        <v>-12.3</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="K28" s="14">
-        <v>43.4</v>
-      </c>
-      <c r="L28" s="13">
-        <v>7.1</v>
+        <v>3.4</v>
+      </c>
+      <c r="L28" s="15">
+        <v>16.899999999999999</v>
       </c>
       <c r="M28" s="14">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="N28" s="15">
-        <v>-46.2</v>
+        <v>2.36</v>
       </c>
       <c r="O28" s="15">
-        <v>-12.3</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="P28" s="14">
-        <v>43.4</v>
-      </c>
-      <c r="Q28" s="13">
-        <v>7.1</v>
+        <v>3.4</v>
+      </c>
+      <c r="Q28" s="15">
+        <v>16.899999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>45231</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>17</v>
+        <v>45261</v>
+      </c>
+      <c r="B29" s="6">
+        <v>142.5</v>
+      </c>
+      <c r="C29" s="6">
+        <v>121</v>
+      </c>
+      <c r="D29" s="6">
+        <v>165</v>
+      </c>
+      <c r="E29" s="6">
+        <v>120</v>
+      </c>
+      <c r="F29" s="9">
+        <v>31</v>
+      </c>
+      <c r="G29" s="9">
+        <v>34.44</v>
       </c>
       <c r="H29" s="8">
-        <v>6.21</v>
-      </c>
-      <c r="I29" s="9">
-        <v>71</v>
-      </c>
-      <c r="J29" s="9">
-        <v>8.35</v>
+        <v>3.34</v>
+      </c>
+      <c r="I29" s="7">
+        <v>-46.2</v>
+      </c>
+      <c r="J29" s="7">
+        <v>-12.3</v>
       </c>
       <c r="K29" s="8">
-        <v>40.049999999999997</v>
+        <v>43.4</v>
       </c>
       <c r="L29" s="9">
-        <v>9.11</v>
+        <v>7.1</v>
       </c>
       <c r="M29" s="8">
-        <v>6.21</v>
-      </c>
-      <c r="N29" s="9">
-        <v>71</v>
-      </c>
-      <c r="O29" s="9">
-        <v>8.35</v>
+        <v>3.34</v>
+      </c>
+      <c r="N29" s="7">
+        <v>-46.2</v>
+      </c>
+      <c r="O29" s="7">
+        <v>-12.3</v>
       </c>
       <c r="P29" s="8">
-        <v>40.049999999999997</v>
+        <v>43.4</v>
       </c>
       <c r="Q29" s="9">
-        <v>9.11</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>17</v>
@@ -2769,39 +2769,39 @@
         <v>17</v>
       </c>
       <c r="H30" s="14">
-        <v>3.63</v>
+        <v>6.21</v>
       </c>
       <c r="I30" s="15">
-        <v>-4.91</v>
+        <v>71</v>
       </c>
       <c r="J30" s="15">
-        <v>-1.37</v>
+        <v>8.35</v>
       </c>
       <c r="K30" s="14">
-        <v>33.85</v>
-      </c>
-      <c r="L30" s="13">
-        <v>9.26</v>
+        <v>40.049999999999997</v>
+      </c>
+      <c r="L30" s="15">
+        <v>9.11</v>
       </c>
       <c r="M30" s="14">
-        <v>3.63</v>
+        <v>6.21</v>
       </c>
       <c r="N30" s="15">
-        <v>-4.91</v>
+        <v>71</v>
       </c>
       <c r="O30" s="15">
-        <v>-1.37</v>
+        <v>8.35</v>
       </c>
       <c r="P30" s="14">
-        <v>33.85</v>
-      </c>
-      <c r="Q30" s="13">
-        <v>9.26</v>
+        <v>40.049999999999997</v>
+      </c>
+      <c r="Q30" s="15">
+        <v>9.11</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>17</v>
@@ -2822,39 +2822,39 @@
         <v>17</v>
       </c>
       <c r="H31" s="8">
-        <v>3.82</v>
-      </c>
-      <c r="I31" s="9">
-        <v>12.5</v>
-      </c>
-      <c r="J31" s="9">
-        <v>14.7</v>
+        <v>3.63</v>
+      </c>
+      <c r="I31" s="7">
+        <v>-4.91</v>
+      </c>
+      <c r="J31" s="7">
+        <v>-1.37</v>
       </c>
       <c r="K31" s="8">
-        <v>30.22</v>
+        <v>33.85</v>
       </c>
       <c r="L31" s="9">
-        <v>10.7</v>
+        <v>9.26</v>
       </c>
       <c r="M31" s="8">
-        <v>3.82</v>
-      </c>
-      <c r="N31" s="9">
-        <v>12.5</v>
-      </c>
-      <c r="O31" s="9">
-        <v>14.7</v>
+        <v>3.63</v>
+      </c>
+      <c r="N31" s="7">
+        <v>-4.91</v>
+      </c>
+      <c r="O31" s="7">
+        <v>-1.37</v>
       </c>
       <c r="P31" s="8">
-        <v>30.22</v>
+        <v>33.85</v>
       </c>
       <c r="Q31" s="9">
-        <v>10.7</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>17</v>
@@ -2875,39 +2875,39 @@
         <v>17</v>
       </c>
       <c r="H32" s="14">
-        <v>3.4</v>
-      </c>
-      <c r="I32" s="13">
-        <v>6.39</v>
-      </c>
-      <c r="J32" s="13">
-        <v>9.51</v>
+        <v>3.82</v>
+      </c>
+      <c r="I32" s="15">
+        <v>12.5</v>
+      </c>
+      <c r="J32" s="15">
+        <v>14.7</v>
       </c>
       <c r="K32" s="14">
-        <v>26.39</v>
-      </c>
-      <c r="L32" s="13">
-        <v>10.1</v>
+        <v>30.22</v>
+      </c>
+      <c r="L32" s="15">
+        <v>10.7</v>
       </c>
       <c r="M32" s="14">
-        <v>3.4</v>
-      </c>
-      <c r="N32" s="13">
-        <v>6.39</v>
-      </c>
-      <c r="O32" s="13">
-        <v>9.51</v>
+        <v>3.82</v>
+      </c>
+      <c r="N32" s="15">
+        <v>12.5</v>
+      </c>
+      <c r="O32" s="15">
+        <v>14.7</v>
       </c>
       <c r="P32" s="14">
-        <v>26.39</v>
-      </c>
-      <c r="Q32" s="13">
-        <v>10.1</v>
+        <v>30.22</v>
+      </c>
+      <c r="Q32" s="15">
+        <v>10.7</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>17</v>
@@ -2928,39 +2928,39 @@
         <v>17</v>
       </c>
       <c r="H33" s="8">
-        <v>3.19</v>
-      </c>
-      <c r="I33" s="7">
-        <v>-19.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="I33" s="9">
+        <v>6.39</v>
       </c>
       <c r="J33" s="9">
-        <v>3.62</v>
+        <v>9.51</v>
       </c>
       <c r="K33" s="8">
-        <v>23</v>
+        <v>26.39</v>
       </c>
       <c r="L33" s="9">
-        <v>10.199999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="M33" s="8">
-        <v>3.19</v>
-      </c>
-      <c r="N33" s="7">
-        <v>-19.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="N33" s="9">
+        <v>6.39</v>
       </c>
       <c r="O33" s="9">
-        <v>3.62</v>
+        <v>9.51</v>
       </c>
       <c r="P33" s="8">
-        <v>23</v>
+        <v>26.39</v>
       </c>
       <c r="Q33" s="9">
-        <v>10.199999999999999</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>17</v>
@@ -2981,39 +2981,39 @@
         <v>17</v>
       </c>
       <c r="H34" s="14">
-        <v>3.97</v>
+        <v>3.19</v>
       </c>
       <c r="I34" s="13">
-        <v>3.4</v>
-      </c>
-      <c r="J34" s="13">
-        <v>15.8</v>
+        <v>-19.5</v>
+      </c>
+      <c r="J34" s="15">
+        <v>3.62</v>
       </c>
       <c r="K34" s="14">
-        <v>19.8</v>
-      </c>
-      <c r="L34" s="13">
-        <v>11.4</v>
+        <v>23</v>
+      </c>
+      <c r="L34" s="15">
+        <v>10.199999999999999</v>
       </c>
       <c r="M34" s="14">
-        <v>3.97</v>
+        <v>3.19</v>
       </c>
       <c r="N34" s="13">
-        <v>3.4</v>
-      </c>
-      <c r="O34" s="13">
-        <v>15.8</v>
+        <v>-19.5</v>
+      </c>
+      <c r="O34" s="15">
+        <v>3.62</v>
       </c>
       <c r="P34" s="14">
-        <v>19.8</v>
-      </c>
-      <c r="Q34" s="13">
-        <v>11.4</v>
+        <v>23</v>
+      </c>
+      <c r="Q34" s="15">
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>17</v>
@@ -3034,39 +3034,39 @@
         <v>17</v>
       </c>
       <c r="H35" s="8">
-        <v>3.84</v>
+        <v>3.97</v>
       </c>
       <c r="I35" s="9">
-        <v>37.799999999999997</v>
+        <v>3.4</v>
       </c>
       <c r="J35" s="9">
-        <v>9.7100000000000009</v>
+        <v>15.8</v>
       </c>
       <c r="K35" s="8">
-        <v>15.83</v>
+        <v>19.8</v>
       </c>
       <c r="L35" s="9">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="M35" s="8">
-        <v>3.84</v>
+        <v>3.97</v>
       </c>
       <c r="N35" s="9">
-        <v>37.799999999999997</v>
+        <v>3.4</v>
       </c>
       <c r="O35" s="9">
-        <v>9.7100000000000009</v>
+        <v>15.8</v>
       </c>
       <c r="P35" s="8">
-        <v>15.83</v>
+        <v>19.8</v>
       </c>
       <c r="Q35" s="9">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>17</v>
@@ -3087,39 +3087,39 @@
         <v>17</v>
       </c>
       <c r="H36" s="14">
-        <v>2.79</v>
+        <v>3.84</v>
       </c>
       <c r="I36" s="15">
-        <v>-20.2</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="J36" s="15">
-        <v>-3.16</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="K36" s="14">
-        <v>11.99</v>
-      </c>
-      <c r="L36" s="13">
-        <v>10.5</v>
+        <v>15.83</v>
+      </c>
+      <c r="L36" s="15">
+        <v>10.3</v>
       </c>
       <c r="M36" s="14">
-        <v>2.79</v>
+        <v>3.84</v>
       </c>
       <c r="N36" s="15">
-        <v>-20.2</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="O36" s="15">
-        <v>-3.16</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="P36" s="14">
-        <v>11.99</v>
-      </c>
-      <c r="Q36" s="13">
-        <v>10.5</v>
+        <v>15.83</v>
+      </c>
+      <c r="Q36" s="15">
+        <v>10.3</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>17</v>
@@ -3140,39 +3140,39 @@
         <v>17</v>
       </c>
       <c r="H37" s="8">
-        <v>3.49</v>
-      </c>
-      <c r="I37" s="9">
-        <v>24.2</v>
+        <v>2.79</v>
+      </c>
+      <c r="I37" s="7">
+        <v>-20.2</v>
       </c>
       <c r="J37" s="7">
-        <v>-5.04</v>
+        <v>-3.16</v>
       </c>
       <c r="K37" s="8">
-        <v>9.2100000000000009</v>
+        <v>11.99</v>
       </c>
       <c r="L37" s="9">
-        <v>15.4</v>
+        <v>10.5</v>
       </c>
       <c r="M37" s="8">
-        <v>3.49</v>
-      </c>
-      <c r="N37" s="9">
-        <v>24.2</v>
+        <v>2.79</v>
+      </c>
+      <c r="N37" s="7">
+        <v>-20.2</v>
       </c>
       <c r="O37" s="7">
-        <v>-5.04</v>
+        <v>-3.16</v>
       </c>
       <c r="P37" s="8">
-        <v>9.2100000000000009</v>
+        <v>11.99</v>
       </c>
       <c r="Q37" s="9">
-        <v>15.4</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>17</v>
@@ -3193,39 +3193,39 @@
         <v>17</v>
       </c>
       <c r="H38" s="14">
-        <v>2.81</v>
+        <v>3.49</v>
       </c>
       <c r="I38" s="15">
-        <v>-3.41</v>
+        <v>24.2</v>
       </c>
       <c r="J38" s="13">
-        <v>13.4</v>
+        <v>-5.04</v>
       </c>
       <c r="K38" s="14">
-        <v>5.72</v>
-      </c>
-      <c r="L38" s="13">
-        <v>32.9</v>
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="L38" s="15">
+        <v>15.4</v>
       </c>
       <c r="M38" s="14">
-        <v>2.81</v>
+        <v>3.49</v>
       </c>
       <c r="N38" s="15">
-        <v>-3.41</v>
+        <v>24.2</v>
       </c>
       <c r="O38" s="13">
-        <v>13.4</v>
+        <v>-5.04</v>
       </c>
       <c r="P38" s="14">
-        <v>5.72</v>
-      </c>
-      <c r="Q38" s="13">
-        <v>32.9</v>
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="Q38" s="15">
+        <v>15.4</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>44927</v>
+        <v>44958</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>17</v>
@@ -3246,39 +3246,39 @@
         <v>17</v>
       </c>
       <c r="H39" s="8">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="I39" s="7">
-        <v>-23.3</v>
+        <v>-3.41</v>
       </c>
       <c r="J39" s="9">
-        <v>59.4</v>
+        <v>13.4</v>
       </c>
       <c r="K39" s="8">
-        <v>2.91</v>
+        <v>5.72</v>
       </c>
       <c r="L39" s="9">
-        <v>59.4</v>
+        <v>32.9</v>
       </c>
       <c r="M39" s="8">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="N39" s="7">
-        <v>-23.3</v>
+        <v>-3.41</v>
       </c>
       <c r="O39" s="9">
-        <v>59.4</v>
+        <v>13.4</v>
       </c>
       <c r="P39" s="8">
-        <v>2.91</v>
+        <v>5.72</v>
       </c>
       <c r="Q39" s="9">
-        <v>59.4</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>17</v>
@@ -3299,39 +3299,39 @@
         <v>17</v>
       </c>
       <c r="H40" s="14">
-        <v>3.81</v>
-      </c>
-      <c r="I40" s="15">
-        <v>-33.5</v>
-      </c>
-      <c r="J40" s="13">
-        <v>86</v>
+        <v>2.91</v>
+      </c>
+      <c r="I40" s="13">
+        <v>-23.3</v>
+      </c>
+      <c r="J40" s="15">
+        <v>59.4</v>
       </c>
       <c r="K40" s="14">
-        <v>40.520000000000003</v>
-      </c>
-      <c r="L40" s="13">
-        <v>63</v>
+        <v>2.91</v>
+      </c>
+      <c r="L40" s="15">
+        <v>59.4</v>
       </c>
       <c r="M40" s="14">
-        <v>3.81</v>
-      </c>
-      <c r="N40" s="15">
-        <v>-33.5</v>
-      </c>
-      <c r="O40" s="13">
-        <v>86</v>
+        <v>2.91</v>
+      </c>
+      <c r="N40" s="13">
+        <v>-23.3</v>
+      </c>
+      <c r="O40" s="15">
+        <v>59.4</v>
       </c>
       <c r="P40" s="14">
-        <v>40.520000000000003</v>
-      </c>
-      <c r="Q40" s="13">
-        <v>63</v>
+        <v>2.91</v>
+      </c>
+      <c r="Q40" s="15">
+        <v>59.4</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>17</v>
@@ -3352,39 +3352,39 @@
         <v>17</v>
       </c>
       <c r="H41" s="8">
-        <v>5.73</v>
-      </c>
-      <c r="I41" s="9">
-        <v>54.6</v>
+        <v>3.81</v>
+      </c>
+      <c r="I41" s="7">
+        <v>-33.5</v>
       </c>
       <c r="J41" s="9">
-        <v>70.8</v>
+        <v>86</v>
       </c>
       <c r="K41" s="8">
-        <v>36.71</v>
+        <v>40.520000000000003</v>
       </c>
       <c r="L41" s="9">
-        <v>51.9</v>
+        <v>63</v>
       </c>
       <c r="M41" s="8">
-        <v>5.73</v>
-      </c>
-      <c r="N41" s="9">
-        <v>54.6</v>
+        <v>3.81</v>
+      </c>
+      <c r="N41" s="7">
+        <v>-33.5</v>
       </c>
       <c r="O41" s="9">
-        <v>70.8</v>
+        <v>86</v>
       </c>
       <c r="P41" s="8">
-        <v>36.71</v>
+        <v>40.520000000000003</v>
       </c>
       <c r="Q41" s="9">
-        <v>51.9</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>17</v>
@@ -3405,86 +3405,139 @@
         <v>17</v>
       </c>
       <c r="H42" s="14">
-        <v>3.68</v>
-      </c>
-      <c r="I42" s="13">
-        <v>13.4</v>
-      </c>
-      <c r="J42" s="13">
-        <v>69.8</v>
+        <v>5.73</v>
+      </c>
+      <c r="I42" s="15">
+        <v>54.6</v>
+      </c>
+      <c r="J42" s="15">
+        <v>70.8</v>
       </c>
       <c r="K42" s="14">
-        <v>30.98</v>
-      </c>
-      <c r="L42" s="13">
-        <v>48.9</v>
+        <v>36.71</v>
+      </c>
+      <c r="L42" s="15">
+        <v>51.9</v>
       </c>
       <c r="M42" s="14">
-        <v>3.68</v>
-      </c>
-      <c r="N42" s="13">
-        <v>13.4</v>
-      </c>
-      <c r="O42" s="13">
-        <v>69.8</v>
+        <v>5.73</v>
+      </c>
+      <c r="N42" s="15">
+        <v>54.6</v>
+      </c>
+      <c r="O42" s="15">
+        <v>70.8</v>
       </c>
       <c r="P42" s="14">
-        <v>30.98</v>
-      </c>
-      <c r="Q42" s="13">
-        <v>48.9</v>
+        <v>36.71</v>
+      </c>
+      <c r="Q42" s="15">
+        <v>51.9</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
+        <v>44835</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="8">
+        <v>3.68</v>
+      </c>
+      <c r="I43" s="9">
+        <v>13.4</v>
+      </c>
+      <c r="J43" s="9">
+        <v>69.8</v>
+      </c>
+      <c r="K43" s="8">
+        <v>30.98</v>
+      </c>
+      <c r="L43" s="9">
+        <v>48.9</v>
+      </c>
+      <c r="M43" s="8">
+        <v>3.68</v>
+      </c>
+      <c r="N43" s="9">
+        <v>13.4</v>
+      </c>
+      <c r="O43" s="9">
+        <v>69.8</v>
+      </c>
+      <c r="P43" s="8">
+        <v>30.98</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="11">
         <v>44805</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" s="8">
+      <c r="B44" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="14">
         <v>3.33</v>
       </c>
-      <c r="I43" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="9">
+      <c r="I44" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="15">
         <v>26.1</v>
       </c>
-      <c r="K43" s="8">
+      <c r="K44" s="14">
         <v>27.3</v>
       </c>
-      <c r="L43" s="9">
+      <c r="L44" s="15">
         <v>46.5</v>
       </c>
-      <c r="M43" s="8">
+      <c r="M44" s="14">
         <v>3.33</v>
       </c>
-      <c r="N43" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="O43" s="9">
+      <c r="N44" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="O44" s="15">
         <v>26.1</v>
       </c>
-      <c r="P43" s="8">
+      <c r="P44" s="14">
         <v>27.3</v>
       </c>
-      <c r="Q43" s="9">
+      <c r="Q44" s="15">
         <v>46.5</v>
       </c>
     </row>
